--- a/data/historial/2026-07-07.xlsx
+++ b/data/historial/2026-07-07.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Desktop\Reportes Ventas Rap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5084D36F-AD4B-4F0D-9F3B-AA36D483AF90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA2F34E-7103-4699-A92F-D1FD80917D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COMISIONES" sheetId="7" r:id="rId1"/>
@@ -27561,7 +27561,7 @@
       </c>
       <c r="C2" s="133"/>
       <c r="D2" s="133">
-        <v>0.18081018518518518</v>
+        <v>0.19258680555555552</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -27573,7 +27573,7 @@
       </c>
       <c r="C3" s="133"/>
       <c r="D3" s="133">
-        <v>0.2487538580246913</v>
+        <v>0.25672646604938271</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -27585,7 +27585,7 @@
       </c>
       <c r="C4" s="133"/>
       <c r="D4" s="133">
-        <v>0.22983796296296291</v>
+        <v>0.22648726851851853</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -27597,7 +27597,7 @@
       </c>
       <c r="C5" s="133"/>
       <c r="D5" s="133">
-        <v>0.23795524691358025</v>
+        <v>0.24355516975308639</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -27609,7 +27609,7 @@
       </c>
       <c r="C6" s="133"/>
       <c r="D6" s="133">
-        <v>0.2056905864197531</v>
+        <v>0.16032214506172843</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -27621,7 +27621,7 @@
       </c>
       <c r="C7" s="133"/>
       <c r="D7" s="133">
-        <v>0.25648148148148153</v>
+        <v>0.24536458333333339</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -27633,7 +27633,7 @@
       </c>
       <c r="C8" s="133"/>
       <c r="D8" s="133">
-        <v>0.22056712962962963</v>
+        <v>0.21192708333333332</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -27645,7 +27645,7 @@
       </c>
       <c r="C9" s="133"/>
       <c r="D9" s="133">
-        <v>0.24519675925925929</v>
+        <v>0.23174768518518524</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -27657,7 +27657,7 @@
       </c>
       <c r="C10" s="133"/>
       <c r="D10" s="133">
-        <v>5.8067129629629621E-2</v>
+        <v>0.10064236111111113</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -27669,7 +27669,7 @@
       </c>
       <c r="C11" s="133"/>
       <c r="D11" s="133">
-        <v>0.23559027777777777</v>
+        <v>0.25892361111111117</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -27681,7 +27681,7 @@
       </c>
       <c r="C12" s="133"/>
       <c r="D12" s="133">
-        <v>0.25729552469135808</v>
+        <v>0.29345679012345682</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -27693,7 +27693,7 @@
       </c>
       <c r="C13" s="133"/>
       <c r="D13" s="133">
-        <v>0.17037808641975313</v>
+        <v>0.19782793209876542</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -27705,7 +27705,7 @@
       </c>
       <c r="C14" s="133"/>
       <c r="D14" s="133">
-        <v>0.25842978395061728</v>
+        <v>0.25936535493827162</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -27717,7 +27717,7 @@
       </c>
       <c r="C15" s="133"/>
       <c r="D15" s="133">
-        <v>0.22162422839506171</v>
+        <v>0.25532021604938271</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -27729,7 +27729,7 @@
       </c>
       <c r="C16" s="133"/>
       <c r="D16" s="133">
-        <v>0.24042824074074079</v>
+        <v>0.21392361111111113</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -27741,7 +27741,7 @@
       </c>
       <c r="C17" s="133"/>
       <c r="D17" s="133">
-        <v>0.2391550925925926</v>
+        <v>0.22774305555555552</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -27753,7 +27753,7 @@
       </c>
       <c r="C18" s="133"/>
       <c r="D18" s="133">
-        <v>0.24932098765432106</v>
+        <v>0.26209683641975307</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -27765,7 +27765,7 @@
       </c>
       <c r="C19" s="133"/>
       <c r="D19" s="133">
-        <v>0.22244212962962964</v>
+        <v>0.24865740740740738</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -27777,7 +27777,7 @@
       </c>
       <c r="C20" s="133"/>
       <c r="D20" s="133">
-        <v>0.28427083333333331</v>
+        <v>0.30322916666666666</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -27789,7 +27789,7 @@
       </c>
       <c r="C21" s="133"/>
       <c r="D21" s="133">
-        <v>0.22618441358024696</v>
+        <v>0.27453317901234575</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -27801,7 +27801,7 @@
       </c>
       <c r="C22" s="133"/>
       <c r="D22" s="133">
-        <v>0.2268634259259259</v>
+        <v>0.25718750000000001</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -27813,7 +27813,7 @@
       </c>
       <c r="C23" s="133"/>
       <c r="D23" s="133">
-        <v>0.20405478395061735</v>
+        <v>0.2125945216049383</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -27825,7 +27825,7 @@
       </c>
       <c r="C24" s="133"/>
       <c r="D24" s="133">
-        <v>0.26149691358024696</v>
+        <v>0.24804012345679019</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -27837,7 +27837,7 @@
       </c>
       <c r="C25" s="133"/>
       <c r="D25" s="133">
-        <v>0.19172453703703715</v>
+        <v>0.19887152777777783</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -27849,7 +27849,7 @@
       </c>
       <c r="C26" s="133"/>
       <c r="D26" s="133">
-        <v>0.2330246913580247</v>
+        <v>0.23207368827160496</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -27861,7 +27861,7 @@
       </c>
       <c r="C27" s="133"/>
       <c r="D27" s="133">
-        <v>0.2512152777777778</v>
+        <v>0.27261574074074069</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -27873,7 +27873,7 @@
       </c>
       <c r="C28" s="133"/>
       <c r="D28" s="133">
-        <v>0.17479552469135803</v>
+        <v>0.24496720679012346</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -27885,7 +27885,7 @@
       </c>
       <c r="C29" s="133"/>
       <c r="D29" s="133">
-        <v>0.19096064814814814</v>
+        <v>0.19471064814814815</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -27897,7 +27897,7 @@
       </c>
       <c r="C30" s="133"/>
       <c r="D30" s="133">
-        <v>0.13555169753086418</v>
+        <v>0.18377700617283949</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -27909,7 +27909,7 @@
       </c>
       <c r="C31" s="133"/>
       <c r="D31" s="133">
-        <v>0.16794367283950615</v>
+        <v>0.16908179012345681</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -27921,7 +27921,7 @@
       </c>
       <c r="C32" s="133"/>
       <c r="D32" s="133">
-        <v>0.18731095679012344</v>
+        <v>0.17693672839506164</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -27933,7 +27933,7 @@
       </c>
       <c r="C33" s="133"/>
       <c r="D33" s="133">
-        <v>0.17720679012345678</v>
+        <v>0.19307677469135798</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="C34" s="133"/>
       <c r="D34" s="133">
-        <v>0.15400077160493827</v>
+        <v>0.11439621913580246</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -27957,7 +27957,7 @@
       </c>
       <c r="C35" s="133"/>
       <c r="D35" s="133">
-        <v>0.10020833333333336</v>
+        <v>0.12538773148148147</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -27969,7 +27969,7 @@
       </c>
       <c r="C36" s="133"/>
       <c r="D36" s="133">
-        <v>0.16411265432098762</v>
+        <v>0.14919753086419751</v>
       </c>
     </row>
   </sheetData>
